--- a/data/sxbet/ligas/Liga Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Liga Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,1182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0xdf10d39269b8f4922176dbbe764797143410bb2b5d10f1971950589d7b96c276</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.75999</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1785218065</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6.279733</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0x52237be26e015f37d415a7a74b1efe879776bd03b7c85911692aef464c5c61b9</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.02344</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785217693</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3.379441</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0xae3a54673e846c38aaabbdc20ca3049c53ce40d8db79d5d85585556cc60cf64a</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>52.83</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.5962</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785216981</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>88.603774</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x4e235a9e511e1d8239d26a55764849fc461c24e4a263420eb829c70fabee8117</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>18.7217</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785216973</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>31.731695</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x473a1df68e848184818fc53053b541e8c7f2488e53cc0d76e08d5e9190b9f908</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>29.90292</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785216972</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>50.682915</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x70f78e17558be5ba081d9ab814282d3372e9da966a3aaa6c4ed300c42444ed89</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785216969</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>37.558685</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0xaa02396e8bb543b44c5015490aaab7b4d1ea7af3c5dec2d6f7f55b4d52a268fc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785216968</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>16.949153</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x25cf5f7e320c6378a5c8bacd958e6ffaadadf90e7c00f6a15e92c4f9f0b5029b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785209084</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>10.380488</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xf84a270bf0345ba966197351f609358499391f68d9ec820094d83228f4b6f8a9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785209068</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5.42439</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x591377d6be1902f7c3ca69808c2f580f367bef2e314d2686337ca852e8b9150c</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785209011</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13.814634</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>0xffd8b4f29a11a927bd73f04ba1fb11aece522f35d3cd449591ed6067b75fdd94</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>4.81482</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1.325</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>San Lorenzo de Almagro</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>0xfc9c2d415cb9ac9c8405af7288d04b71501bfd44f96ae6045e8ee4b6c621607b</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>L19492342</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1785186963</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>1785276000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>14.814831</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Liga Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Liga Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xdf10d39269b8f4922176dbbe764797143410bb2b5d10f1971950589d7b96c276</t>
+          <t>0xe40648e0e8222c1f67213f3d1436fe12a1ce6b44e8a69bf8616ea37e5b20e550</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.75999</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>San Lorenzo de Almagro</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0xf49160916b9eccdfe85b038286d333d282bfc5d5e78fabbc30124b9bc18a8d5a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19492342</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785218065</t>
+          <t>1785239978</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785284100</t>
+          <t>1785276000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6.279733</t>
+          <t>69.856813</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x52237be26e015f37d415a7a74b1efe879776bd03b7c85911692aef464c5c61b9</t>
+          <t>0xdab55b92c40bb630709b1c58d8792ba6e4859d1d831635170fa22a9cd10b71e1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,12 +646,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02344</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785217693</t>
+          <t>1785239062</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.379441</t>
+          <t>3.319502</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xae3a54673e846c38aaabbdc20ca3049c53ce40d8db79d5d85585556cc60cf64a</t>
+          <t>0x7320cc14b90acfa8cfa3faf78417a39d1478d168c0508af23d4b9c46f7a51880</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,23 +747,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -771,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785216981</t>
+          <t>1785238994</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>88.603774</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4e235a9e511e1d8239d26a55764849fc461c24e4a263420eb829c70fabee8117</t>
+          <t>0xb9f8b5a2cb5c3a70c71c49c98d4f9e28eb8a1d910353dd9f430f81eb3560117a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -851,15 +859,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18.7217</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -867,7 +879,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -920,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785216973</t>
+          <t>1785238969</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>31.731695</t>
+          <t>38.979228</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,31 +963,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x473a1df68e848184818fc53053b541e8c7f2488e53cc0d76e08d5e9190b9f908</t>
+          <t>0xfeff576bc7aedfdf0ffd89ead6388459e417dbe76af740a3e1d991561699a730</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29.90292</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -979,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785216972</t>
+          <t>1785238952</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>50.682915</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x70f78e17558be5ba081d9ab814282d3372e9da966a3aaa6c4ed300c42444ed89</t>
+          <t>0x383ea02d7178b56388f8c05841af51520a84bd16ff5cd342cc75ed469ae54eb6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1066,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors -1.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1091,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785216969</t>
+          <t>1785238908</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37.558685</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xaa02396e8bb543b44c5015490aaab7b4d1ea7af3c5dec2d6f7f55b4d52a268fc</t>
+          <t>0xb7a6ecc1b41c8e698ab08e80596407b2e70b3cc8d4b8bc53bb57ea18e2c9aebf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1171,23 +1195,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -1195,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785216968</t>
+          <t>1785238887</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>16.949153</t>
+          <t>14.857143</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,12 +1299,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x25cf5f7e320c6378a5c8bacd958e6ffaadadf90e7c00f6a15e92c4f9f0b5029b</t>
+          <t>0xc2eea158b7e84c7049269ff7fc0bfd2c3b9c6dc96086b244e2b9047935848949</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1282,22 +1314,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors -1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1307,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785209084</t>
+          <t>1785238885</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>10.380488</t>
+          <t>23.299145</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf84a270bf0345ba966197351f609358499391f68d9ec820094d83228f4b6f8a9</t>
+          <t>0xf66256212dcba2f08ffb119c3cf1982fc22e85af7e7e4804144b97bf7a6640fc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1394,22 +1426,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors -1.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1419,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1464,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785209068</t>
+          <t>1785238875</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>5.42439</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,12 +1523,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x591377d6be1902f7c3ca69808c2f580f367bef2e314d2686337ca852e8b9150c</t>
+          <t>0xb4072d9b8acae890cd70526a6703ffc3ee84d263741a803f65b79911bbe2e5a6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1506,12 +1538,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>67.65</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1521,7 +1553,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1531,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785209011</t>
+          <t>1785238874</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13.814634</t>
+          <t>96.815742</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,110 +1635,3758 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>0x46ef4c4aa81117b842ff87805ee386f9cabde3eac464d000a7c3ff0a6b8b2ebb</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>28.13639</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.585</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19493059</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785238874</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>48.096393</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x39a23d78da04d0ec02d55f22da06103e1d235efe6e55a1cdccf11ed5466a002c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>314.34999</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.6987</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19493059</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785238873</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>449.874762</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0xb2e97bfcbc9bca9ddcbe6c10c9cb1b120a9c1f916d7fe27835634427d14d29a8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.5913</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785238752</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>10.350951</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x7a385488ce792c84e52c1d4a34bb4805456c705b6170732fd2c2b49338c75804</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>680.905</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19493059</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785238631</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1275.700234</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x9ec229fa5e95f172f9f957edd68d92078ec94766e796386d40507038bf63d0b4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>680.905</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.5337</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19493059</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785238630</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1275.700234</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xc9965f577194e6482fc6558fa224ee9314b4154d276fb133a213c0080b2d5276</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>34.59999</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.5587</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19493059</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785238629</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>61.923919</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x24f5d12e8af98179ec858efffec4d524511ffd2a7d9b667ddec8efe015f48bbe</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>12.90769</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.395</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19493059</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785238629</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>32.677696</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x6d67ce8c184fa4ad81a6e22e992da94fc9d686c63ef97c07d2e5c60440433bd9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.00376</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.4163</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785237631</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0.009033</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x0adbe7357efdd21f0cce308f7dabce9dce9b8c24ae0df9c25134b53d1a807bf9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>287.99625</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.4163</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785237631</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>691.882883</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x6b2e3ec88eea3e8bca932c953defd80211f8124eab3a507716f0b752cfdebe76</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>29.47904</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.6125</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785237630</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>48.129045</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0xa1f7256d718b701e04faa9a1431e991fc8b56fd1a2d67728d39b32fc2bc83dc8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>16.30999</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.6825</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x7ee7a0c56bac1d1bec7e1cd6d99a13b6f3b8f571afd22abdb797389583b3285e</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785237246</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>23.897421</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xda3fb02c3f5653973c9187e7fa4eeeface0cdbb85de0d17190304582f02778a9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>282.16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.2763</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785236772</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1021.393665</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xa9dbfc58c6e934609b29453822b6fd4ee960f842174bf0d6d67960f03193ec3f</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4.4366</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.4213</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia vs Huracan</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Huracan</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x7f314b676ac8f6edae99214062514796a773d6b2a1d11ebc8c98d020b75f6755</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19511048</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785236516</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785448800</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>10.531988</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x42c4cd1ef479d774202b60b74d44d8aab9c7cde631134696c10ebfaacf10c25b</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.1167</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.4537</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Barracas Central vs Aldosivi</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0xa1b1ce18a36591bb74e00ed5a3084d2b6ece0140d77866202206d5b241018085</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19499796</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785236503</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785346200</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>0.25719</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0xcc87cce8a372439dfbbed8a41cd90bd1f2374b1ec4ae926751fbc3aa231f2113</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4.0014</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.3262</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>San Lorenzo de Almagro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Atletico Gimnasia y Esgrima de Mendoza</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x9f121d6ffd0dd7b3ee2fdfa823180709991d51cb157a826f16de4cfb1778a642</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19492342</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785236488</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785276000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12.264828</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xf51253e09509e29550ac64485b2633fc2a45dfb49a63f46d31ebb4dbaa5559df</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4.6681</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.3388</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Banfield vs Club Atletico Sarmiento De Junin</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Club Atletico Sarmiento De Junin</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x0552e2f5c74df172a91b02bc75d9102ef0a4a19573eec6fe68007bb675d7bdb5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19492343</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785236482</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785276000</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13.780369</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x87632f3c09cfe931a4f8a5e88dce8173e3ec0c9412b1eb1350f1f61bf85a1f19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.5387</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Banfield vs Club Atletico Sarmiento De Junin</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Club Atletico Sarmiento De Junin</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x2b10d780a83b66a6da508305dbade07b24d8a26ecfd288b044d25d639328ed26</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19492343</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785234101</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785276000</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.911833</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xbb97f6964cd2ae270604d348c7c6f9f47b55ce4843079bb8464eac95d6d9a29b</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.415</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785221642</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>4.987952</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xfee30673fe652fdf43fc060fb8b970e5d0039f29a866bf29c8e32f7593a05244</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.4112</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785221633</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>4.49848</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x6e026b5997adaa13fdfd9b992070291ec5d0fa8e658c58b14ed63f0955432a1e</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>17.76</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4112</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xf015d89a8a1ff1dd23068640169480b5cd556e8da1b87076be62e31dbf8c87d3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785221633</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>43.18541</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x7e80d16e1289158eadbef76159663eda4afd1866bbd1256236847795aeeee44c</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785221620</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>126.851852</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x7f2f1b065a8e90f60365b52470b7db03e15ebcc7f0e5d1697f5ecab3a61b1785</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785221618</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>5.111111</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x4a7c953f7c75b2f4f6a5bc951fb7d6f74352f9c14139b551e74416c1983715ca</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785221217</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>8.350731</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x60dba863a8c4d5e501b056786f811d5b1bff915ae35677252527e84dbfeeb2de</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>24.72594</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785221195</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>41.295933</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xdf10d39269b8f4922176dbbe764797143410bb2b5d10f1971950589d7b96c276</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3.75999</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785218065</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>6.279733</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x52237be26e015f37d415a7a74b1efe879776bd03b7c85911692aef464c5c61b9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.02344</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785217693</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>3.379441</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xae3a54673e846c38aaabbdc20ca3049c53ce40d8db79d5d85585556cc60cf64a</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>52.83</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.5962</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785216981</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>88.603774</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x4e235a9e511e1d8239d26a55764849fc461c24e4a263420eb829c70fabee8117</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>18.7217</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785216973</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>31.731695</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x473a1df68e848184818fc53053b541e8c7f2488e53cc0d76e08d5e9190b9f908</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>29.90292</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785216972</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>50.682915</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x70f78e17558be5ba081d9ab814282d3372e9da966a3aaa6c4ed300c42444ed89</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785216969</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>37.558685</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xaa02396e8bb543b44c5015490aaab7b4d1ea7af3c5dec2d6f7f55b4d52a268fc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785216968</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>16.949153</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x25cf5f7e320c6378a5c8bacd958e6ffaadadf90e7c00f6a15e92c4f9f0b5029b</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785209084</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10.380488</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xf84a270bf0345ba966197351f609358499391f68d9ec820094d83228f4b6f8a9</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785209068</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>5.42439</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x591377d6be1902f7c3ca69808c2f580f367bef2e314d2686337ca852e8b9150c</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785209011</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>13.814634</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>0xffd8b4f29a11a927bd73f04ba1fb11aece522f35d3cd449591ed6067b75fdd94</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>4.81482</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>1.325</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>San Lorenzo de Almagro</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>0xfc9c2d415cb9ac9c8405af7288d04b71501bfd44f96ae6045e8ee4b6c621607b</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>L19492342</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>1785186963</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>1785276000</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>14.814831</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Liga Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Liga Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe40648e0e8222c1f67213f3d1436fe12a1ce6b44e8a69bf8616ea37e5b20e550</t>
+          <t>0x27f6a5f9f8cce0147a6f8d99dff31c38f975624cc3d494f7d49eac634099c793</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>19.43134</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5413</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>San Lorenzo de Almagro</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Atletico Gimnasia y Esgrima de Mendoza</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xf49160916b9eccdfe85b038286d333d282bfc5d5e78fabbc30124b9bc18a8d5a</t>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19492342</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785239978</t>
+          <t>1785241208</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785276000</t>
+          <t>1785284100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>69.856813</t>
+          <t>45.991337</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xdab55b92c40bb630709b1c58d8792ba6e4859d1d831635170fa22a9cd10b71e1</t>
+          <t>0x9347e108761188c43c83e865712e25759d4d6d081bfc135b7030b287af9a085d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785239062</t>
+          <t>1785240932</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.319502</t>
+          <t>45.557895</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x7320cc14b90acfa8cfa3faf78417a39d1478d168c0508af23d4b9c46f7a51880</t>
+          <t>0x6479a0cd88fac93a5c1fbfe1f6af44b79d707ea64e7f1f0b785bca0026ce11ff</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,31 +747,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>113.04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -794,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+          <t>0xdcbb328e4a85b927baf9ec69e3a2ce22638ee6e6eb1b6bf1252508d8596378fe</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785238994</t>
+          <t>1785240930</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>336.178439</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,39 +843,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb9f8b5a2cb5c3a70c71c49c98d4f9e28eb8a1d910353dd9f430f81eb3560117a</t>
+          <t>0x2342484037c3ef4411cc22f5c2dc7e0dce230a0dac2183d0da40d88e5792a23c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>10.58637</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0xdcbb328e4a85b927baf9ec69e3a2ce22638ee6e6eb1b6bf1252508d8596378fe</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785238969</t>
+          <t>1785240930</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>38.979228</t>
+          <t>31.601104</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfeff576bc7aedfdf0ffd89ead6388459e417dbe76af740a3e1d991561699a730</t>
+          <t>0x13d21301d7c4abb60159909fdf001312671939d3558444861b6bd1723822b1cf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -971,31 +955,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.3337</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -1018,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+          <t>0xdcbb328e4a85b927baf9ec69e3a2ce22638ee6e6eb1b6bf1252508d8596378fe</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785238952</t>
+          <t>1785240929</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>31.730337</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x383ea02d7178b56388f8c05841af51520a84bd16ff5cd342cc75ed469ae54eb6</t>
+          <t>0xe40648e0e8222c1f67213f3d1436fe12a1ce6b44e8a69bf8616ea37e5b20e550</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1083,31 +1059,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5413</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors -1.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -1115,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+          <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>San Lorenzo de Almagro</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+          <t>0xf49160916b9eccdfe85b038286d333d282bfc5d5e78fabbc30124b9bc18a8d5a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19493059</t>
+          <t>L19492342</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785238908</t>
+          <t>1785239978</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785284100</t>
+          <t>1785276000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>16.761905</t>
+          <t>69.856813</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,39 +1155,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb7a6ecc1b41c8e698ab08e80596407b2e70b3cc8d4b8bc53bb57ea18e2c9aebf</t>
+          <t>0xdab55b92c40bb630709b1c58d8792ba6e4859d1d831635170fa22a9cd10b71e1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -1242,7 +1202,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785238887</t>
+          <t>1785239062</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>14.857143</t>
+          <t>3.319502</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,12 +1259,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc2eea158b7e84c7049269ff7fc0bfd2c3b9c6dc96086b244e2b9047935848949</t>
+          <t>0x7320cc14b90acfa8cfa3faf78417a39d1478d168c0508af23d4b9c46f7a51880</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1314,22 +1274,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Argentinos Juniors -1</t>
+          <t>Argentinos Juniors -1.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1354,7 +1314,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1384,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785238885</t>
+          <t>1785238994</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1394,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>23.299145</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,12 +1371,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf66256212dcba2f08ffb119c3cf1982fc22e85af7e7e4804144b97bf7a6640fc</t>
+          <t>0xb9f8b5a2cb5c3a70c71c49c98d4f9e28eb8a1d910353dd9f430f81eb3560117a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1426,22 +1386,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Argentinos Juniors -1.5</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1451,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19493059</t>
+          <t>L19493058</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785238875</t>
+          <t>1785238969</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1506,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.380952</t>
+          <t>38.979228</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,12 +1483,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb4072d9b8acae890cd70526a6703ffc3ee84d263741a803f65b79911bbe2e5a6</t>
+          <t>0xfeff576bc7aedfdf0ffd89ead6388459e417dbe76af740a3e1d991561699a730</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1538,39 +1498,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6987</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Argentinos Juniors -1.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Argentinos Juniors</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Estudiantes Rio Cuarto</t>
@@ -1578,7 +1538,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1608,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785238874</t>
+          <t>1785238952</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1618,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>96.815742</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x46ef4c4aa81117b842ff87805ee386f9cabde3eac464d000a7c3ff0a6b8b2ebb</t>
+          <t>0x383ea02d7178b56388f8c05841af51520a84bd16ff5cd342cc75ed469ae54eb6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1650,22 +1610,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28.13639</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Argentinos Juniors -1</t>
+          <t>Argentinos Juniors -1.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1690,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1720,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785238874</t>
+          <t>1785238908</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1730,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.096393</t>
+          <t>16.761905</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,7 +1707,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x39a23d78da04d0ec02d55f22da06103e1d235efe6e55a1cdccf11ed5466a002c</t>
+          <t>0xb7a6ecc1b41c8e698ab08e80596407b2e70b3cc8d4b8bc53bb57ea18e2c9aebf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1762,39 +1722,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>314.34999</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6987</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Argentinos Juniors -1.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Argentinos Juniors</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Argentinos Juniors</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Estudiantes Rio Cuarto</t>
@@ -1802,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1832,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785238873</t>
+          <t>1785238887</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1842,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>449.874762</t>
+          <t>14.857143</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,31 +1819,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xb2e97bfcbc9bca9ddcbe6c10c9cb1b120a9c1f916d7fe27835634427d14d29a8</t>
+          <t>0xc2eea158b7e84c7049269ff7fc0bfd2c3b9c6dc96086b244e2b9047935848949</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -1891,27 +1859,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1936,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785238752</t>
+          <t>1785238885</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1946,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>10.350951</t>
+          <t>23.299145</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,7 +1931,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x7a385488ce792c84e52c1d4a34bb4805456c705b6170732fd2c2b49338c75804</t>
+          <t>0xf66256212dcba2f08ffb119c3cf1982fc22e85af7e7e4804144b97bf7a6640fc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1971,15 +1939,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>680.905</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1987,7 +1959,11 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -2040,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785238631</t>
+          <t>1785238875</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2050,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1275.700234</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2067,31 +2043,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x9ec229fa5e95f172f9f957edd68d92078ec94766e796386d40507038bf63d0b4</t>
+          <t>0xb4072d9b8acae890cd70526a6703ffc3ee84d263741a803f65b79911bbe2e5a6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>680.905</t>
+          <t>67.65</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -2114,7 +2098,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
+          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2144,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785238630</t>
+          <t>1785238874</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1275.700234</t>
+          <t>96.815742</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xc9965f577194e6482fc6558fa224ee9314b4154d276fb133a213c0080b2d5276</t>
+          <t>0x46ef4c4aa81117b842ff87805ee386f9cabde3eac464d000a7c3ff0a6b8b2ebb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2186,12 +2170,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34.59999</t>
+          <t>28.13639</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2256,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785238629</t>
+          <t>1785238874</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2250,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>61.923919</t>
+          <t>48.096393</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,7 +2267,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x24f5d12e8af98179ec858efffec4d524511ffd2a7d9b667ddec8efe015f48bbe</t>
+          <t>0x39a23d78da04d0ec02d55f22da06103e1d235efe6e55a1cdccf11ed5466a002c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2298,22 +2282,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.90769</t>
+          <t>314.34999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Argentinos Juniors -1.5</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2322,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
+          <t>0x91dfa4ba7927a773d1cca3928d381d8d919180e366938f9342f149b220e1b742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2368,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785238629</t>
+          <t>1785238873</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>32.677696</t>
+          <t>449.874762</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,7 +2379,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6d67ce8c184fa4ad81a6e22e992da94fc9d686c63ef97c07d2e5c60440433bd9</t>
+          <t>0xb2e97bfcbc9bca9ddcbe6c10c9cb1b120a9c1f916d7fe27835634427d14d29a8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2403,19 +2387,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.00376</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2423,26 +2403,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Rosario Central</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Racing Club de Avellaneda</t>
@@ -2480,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785237631</t>
+          <t>1785238752</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.009033</t>
+          <t>10.350951</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,7 +2483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x0adbe7357efdd21f0cce308f7dabce9dce9b8c24ae0df9c25134b53d1a807bf9</t>
+          <t>0x7a385488ce792c84e52c1d4a34bb4805456c705b6170732fd2c2b49338c75804</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2515,31 +2491,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>287.99625</t>
+          <t>680.905</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4163</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -2547,27 +2515,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2592,7 +2560,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785237631</t>
+          <t>1785238631</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2602,7 +2570,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>691.882883</t>
+          <t>1275.700234</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,7 +2587,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x6b2e3ec88eea3e8bca932c953defd80211f8124eab3a507716f0b752cfdebe76</t>
+          <t>0x9ec229fa5e95f172f9f957edd68d92078ec94766e796386d40507038bf63d0b4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2627,59 +2595,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29.47904</t>
+          <t>680.905</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>Liga Profesional</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2704,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785237630</t>
+          <t>1785238630</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2714,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.129045</t>
+          <t>1275.700234</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,7 +2691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xa1f7256d718b701e04faa9a1431e991fc8b56fd1a2d67728d39b32fc2bc83dc8</t>
+          <t>0xc9965f577194e6482fc6558fa224ee9314b4154d276fb133a213c0080b2d5276</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2739,23 +2699,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.30999</t>
+          <t>34.59999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors -1</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -2763,27 +2731,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x7ee7a0c56bac1d1bec7e1cd6d99a13b6f3b8f571afd22abdb797389583b3285e</t>
+          <t>0xd7b4f13d15962c2bb7e5cd03fac7428a62a1554a365017db124d843b1aa1ce84</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2808,7 +2776,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785237246</t>
+          <t>1785238629</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2818,7 +2786,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>23.897421</t>
+          <t>61.923919</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,7 +2803,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xda3fb02c3f5653973c9187e7fa4eeeface0cdbb85de0d17190304582f02778a9</t>
+          <t>0x24f5d12e8af98179ec858efffec4d524511ffd2a7d9b667ddec8efe015f48bbe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2850,22 +2818,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>282.16</t>
+          <t>12.90769</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2763</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors -1.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2875,27 +2843,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Argentinos Juniors vs Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x2d5141701171279d64274791c36deb0bbf24270387c165c3e1d0aa427afc3b49</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19493059</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2920,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785236772</t>
+          <t>1785238629</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2930,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1021.393665</t>
+          <t>32.677696</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2947,59 +2915,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xa9dbfc58c6e934609b29453822b6fd4ee960f842174bf0d6d67960f03193ec3f</t>
+          <t>0x6d67ce8c184fa4ad81a6e22e992da94fc9d686c63ef97c07d2e5c60440433bd9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.4366</t>
+          <t>0.00376</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>Liga Profesional</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia vs Huracan</t>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Huracan</t>
+          <t>Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x7f314b676ac8f6edae99214062514796a773d6b2a1d11ebc8c98d020b75f6755</t>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19511048</t>
+          <t>L19493058</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3024,17 +3000,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785236516</t>
+          <t>1785237631</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785448800</t>
+          <t>1785284100</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10.531988</t>
+          <t>0.009033</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3051,59 +3027,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x42c4cd1ef479d774202b60b74d44d8aab9c7cde631134696c10ebfaacf10c25b</t>
+          <t>0x0adbe7357efdd21f0cce308f7dabce9dce9b8c24ae0df9c25134b53d1a807bf9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.1167</t>
+          <t>287.99625</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.4163</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>Liga Profesional</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Barracas Central vs Aldosivi</t>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xa1b1ce18a36591bb74e00ed5a3084d2b6ece0140d77866202206d5b241018085</t>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19499796</t>
+          <t>L19493058</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3128,17 +3112,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785236503</t>
+          <t>1785237631</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785346200</t>
+          <t>1785284100</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.25719</t>
+          <t>691.882883</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3155,23 +3139,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xcc87cce8a372439dfbbed8a41cd90bd1f2374b1ec4ae926751fbc3aa231f2113</t>
+          <t>0x6b2e3ec88eea3e8bca932c953defd80211f8124eab3a507716f0b752cfdebe76</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.0014</t>
+          <t>29.47904</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3179,7 +3167,11 @@
           <t>Liga Profesional</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -3187,27 +3179,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>San Lorenzo de Almagro</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Atletico Gimnasia y Esgrima de Mendoza</t>
+          <t>Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x9f121d6ffd0dd7b3ee2fdfa823180709991d51cb157a826f16de4cfb1778a642</t>
+          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19492342</t>
+          <t>L19493058</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3232,17 +3224,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785236488</t>
+          <t>1785237630</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785276000</t>
+          <t>1785284100</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12.264828</t>
+          <t>48.129045</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,28 +3251,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xf51253e09509e29550ac64485b2633fc2a45dfb49a63f46d31ebb4dbaa5559df</t>
+          <t>0xa1f7256d718b701e04faa9a1431e991fc8b56fd1a2d67728d39b32fc2bc83dc8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.6681</t>
+          <t>16.30999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liga Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3291,27 +3283,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Banfield vs Club Atletico Sarmiento De Junin</t>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Club Atletico Sarmiento De Junin</t>
+          <t>Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x0552e2f5c74df172a91b02bc75d9102ef0a4a19573eec6fe68007bb675d7bdb5</t>
+          <t>0x7ee7a0c56bac1d1bec7e1cd6d99a13b6f3b8f571afd22abdb797389583b3285e</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19492343</t>
+          <t>L19493058</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3336,17 +3328,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785236482</t>
+          <t>1785237246</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785276000</t>
+          <t>1785284100</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13.780369</t>
+          <t>23.897421</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,23 +3355,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x87632f3c09cfe931a4f8a5e88dce8173e3ec0c9412b1eb1350f1f61bf85a1f19</t>
+          <t>0xda3fb02c3f5653973c9187e7fa4eeeface0cdbb85de0d17190304582f02778a9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>282.16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.2763</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3387,7 +3383,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -3395,27 +3395,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Banfield vs Club Atletico Sarmiento De Junin</t>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Club Atletico Sarmiento De Junin</t>
+          <t>Racing Club de Avellaneda</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x2b10d780a83b66a6da508305dbade07b24d8a26ecfd288b044d25d639328ed26</t>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19492343</t>
+          <t>L19493058</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785234101</t>
+          <t>1785236772</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785276000</t>
+          <t>1785284100</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1.911833</t>
+          <t>1021.393665</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3467,23 +3467,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xbb97f6964cd2ae270604d348c7c6f9f47b55ce4843079bb8464eac95d6d9a29b</t>
+          <t>0xa9dbfc58c6e934609b29453822b6fd4ee960f842174bf0d6d67960f03193ec3f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.4366</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3499,27 +3499,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Independiente Rivadavia vs Huracan</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Huracan</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
+          <t>0x7f314b676ac8f6edae99214062514796a773d6b2a1d11ebc8c98d020b75f6755</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19511048</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785221642</t>
+          <t>1785236516</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785284100</t>
+          <t>1785448800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4.987952</t>
+          <t>10.531988</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3571,23 +3571,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xfee30673fe652fdf43fc060fb8b970e5d0039f29a866bf29c8e32f7593a05244</t>
+          <t>0x42c4cd1ef479d774202b60b74d44d8aab9c7cde631134696c10ebfaacf10c25b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.1167</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3603,27 +3603,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Barracas Central vs Aldosivi</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
+          <t>0xa1b1ce18a36591bb74e00ed5a3084d2b6ece0140d77866202206d5b241018085</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19499796</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785221633</t>
+          <t>1785236503</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785284100</t>
+          <t>1785346200</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4.49848</t>
+          <t>0.25719</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3675,23 +3675,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x6e026b5997adaa13fdfd9b992070291ec5d0fa8e658c58b14ed63f0955432a1e</t>
+          <t>0xcc87cce8a372439dfbbed8a41cd90bd1f2374b1ec4ae926751fbc3aa231f2113</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>4.0014</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3707,27 +3707,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>San Lorenzo de Almagro</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xf015d89a8a1ff1dd23068640169480b5cd556e8da1b87076be62e31dbf8c87d3</t>
+          <t>0x9f121d6ffd0dd7b3ee2fdfa823180709991d51cb157a826f16de4cfb1778a642</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19492342</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3752,17 +3752,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785221633</t>
+          <t>1785236488</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785284100</t>
+          <t>1785276000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>43.18541</t>
+          <t>12.264828</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3779,39 +3779,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x7e80d16e1289158eadbef76159663eda4afd1866bbd1256236847795aeeee44c</t>
+          <t>0xf51253e09509e29550ac64485b2633fc2a45dfb49a63f46d31ebb4dbaa5559df</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD65db8c52dE90A5095DBCB8428418a175a05Ad38</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>4.6681</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Racing Club de Avellaneda</t>
-        </is>
-      </c>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -3819,27 +3811,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Banfield vs Club Atletico Sarmiento De Junin</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Club Atletico Sarmiento De Junin</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x0552e2f5c74df172a91b02bc75d9102ef0a4a19573eec6fe68007bb675d7bdb5</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19492343</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3864,17 +3856,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785221620</t>
+          <t>1785236482</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785284100</t>
+          <t>1785276000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>126.851852</t>
+          <t>13.780369</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3891,27 +3883,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x7f2f1b065a8e90f60365b52470b7db03e15ebcc7f0e5d1697f5ecab3a61b1785</t>
+          <t>0x87632f3c09cfe931a4f8a5e88dce8173e3ec0c9412b1eb1350f1f61bf85a1f19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3919,11 +3907,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Racing Club de Avellaneda</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -3931,27 +3915,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
+          <t>Banfield vs Club Atletico Sarmiento De Junin</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Racing Club de Avellaneda</t>
+          <t>Club Atletico Sarmiento De Junin</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x2b10d780a83b66a6da508305dbade07b24d8a26ecfd288b044d25d639328ed26</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19493058</t>
+          <t>L19492343</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3976,17 +3960,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785221618</t>
+          <t>1785234101</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785284100</t>
+          <t>1785276000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>5.111111</t>
+          <t>1.911833</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4003,28 +3987,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x4a7c953f7c75b2f4f6a5bc951fb7d6f74352f9c14139b551e74416c1983715ca</t>
+          <t>0xbb97f6964cd2ae270604d348c7c6f9f47b55ce4843079bb8464eac95d6d9a29b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Liga Profesional</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4050,7 +4034,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4080,7 +4064,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785221217</t>
+          <t>1785221642</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4090,7 +4074,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>8.350731</t>
+          <t>4.987952</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4107,28 +4091,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x60dba863a8c4d5e501b056786f811d5b1bff915ae35677252527e84dbfeeb2de</t>
+          <t>0xfee30673fe652fdf43fc060fb8b970e5d0039f29a866bf29c8e32f7593a05244</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24.72594</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Liga Profesional</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4154,7 +4138,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0x422a07999443d275cb90fc669c3702632b7b28eb8065d685a18261ff11401847</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4184,7 +4168,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785221195</t>
+          <t>1785221633</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4194,7 +4178,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>41.295933</t>
+          <t>4.49848</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4211,7 +4195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xdf10d39269b8f4922176dbbe764797143410bb2b5d10f1971950589d7b96c276</t>
+          <t>0x6e026b5997adaa13fdfd9b992070291ec5d0fa8e658c58b14ed63f0955432a1e</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4222,17 +4206,17 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.75999</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Liga Profesional</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4258,7 +4242,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0xf015d89a8a1ff1dd23068640169480b5cd556e8da1b87076be62e31dbf8c87d3</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4288,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785218065</t>
+          <t>1785221633</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4298,7 +4282,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6.279733</t>
+          <t>43.18541</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,23 +4299,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x52237be26e015f37d415a7a74b1efe879776bd03b7c85911692aef464c5c61b9</t>
+          <t>0x7e80d16e1289158eadbef76159663eda4afd1866bbd1256236847795aeeee44c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.02344</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4339,7 +4327,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -4362,7 +4354,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4392,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785217693</t>
+          <t>1785221620</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>3.379441</t>
+          <t>126.851852</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,7 +4411,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xae3a54673e846c38aaabbdc20ca3049c53ce40d8db79d5d85585556cc60cf64a</t>
+          <t>0x7f2f1b065a8e90f60365b52470b7db03e15ebcc7f0e5d1697f5ecab3a61b1785</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,15 +4419,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4443,7 +4439,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785216981</t>
+          <t>1785221618</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>88.603774</t>
+          <t>5.111111</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,23 +4523,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x4e235a9e511e1d8239d26a55764849fc461c24e4a263420eb829c70fabee8117</t>
+          <t>0x4a7c953f7c75b2f4f6a5bc951fb7d6f74352f9c14139b551e74416c1983715ca</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>18.7217</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785216973</t>
+          <t>1785221217</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>31.731695</t>
+          <t>8.350731</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,7 +4627,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x473a1df68e848184818fc53053b541e8c7f2488e53cc0d76e08d5e9190b9f908</t>
+          <t>0x60dba863a8c4d5e501b056786f811d5b1bff915ae35677252527e84dbfeeb2de</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4638,12 +4638,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>29.90292</t>
+          <t>24.72594</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785216972</t>
+          <t>1785221195</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>50.682915</t>
+          <t>41.295933</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,7 +4731,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x70f78e17558be5ba081d9ab814282d3372e9da966a3aaa6c4ed300c42444ed89</t>
+          <t>0xdf10d39269b8f4922176dbbe764797143410bb2b5d10f1971950589d7b96c276</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4739,19 +4739,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.75999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4759,34 +4755,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Racing Club de Avellaneda</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Racing Club de Avellaneda</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4816,7 +4808,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785216969</t>
+          <t>1785218065</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4826,7 +4818,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>37.558685</t>
+          <t>6.279733</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,23 +4835,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xaa02396e8bb543b44c5015490aaab7b4d1ea7af3c5dec2d6f7f55b4d52a268fc</t>
+          <t>0x52237be26e015f37d415a7a74b1efe879776bd03b7c85911692aef464c5c61b9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.02344</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785216968</t>
+          <t>1785217693</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>16.949153</t>
+          <t>3.379441</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,7 +4939,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x25cf5f7e320c6378a5c8bacd958e6ffaadadf90e7c00f6a15e92c4f9f0b5029b</t>
+          <t>0xae3a54673e846c38aaabbdc20ca3049c53ce40d8db79d5d85585556cc60cf64a</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4955,19 +4947,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>52.83</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4975,34 +4963,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Racing Club de Avellaneda</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Racing Club de Avellaneda</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5032,7 +5016,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785209084</t>
+          <t>1785216981</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5042,7 +5026,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>10.380488</t>
+          <t>88.603774</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5059,27 +5043,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xf84a270bf0345ba966197351f609358499391f68d9ec820094d83228f4b6f8a9</t>
+          <t>0x4e235a9e511e1d8239d26a55764849fc461c24e4a263420eb829c70fabee8117</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>18.7217</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5087,34 +5067,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Racing Club de Avellaneda</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Racing Club de Avellaneda</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5144,7 +5120,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785209068</t>
+          <t>1785216973</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5154,7 +5130,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>5.42439</t>
+          <t>31.731695</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5171,27 +5147,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x591377d6be1902f7c3ca69808c2f580f367bef2e314d2686337ca852e8b9150c</t>
+          <t>0x473a1df68e848184818fc53053b541e8c7f2488e53cc0d76e08d5e9190b9f908</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>29.90292</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5199,34 +5171,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Racing Club de Avellaneda</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Rosario Central vs Racing Club de Avellaneda</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Rosario Central</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Racing Club de Avellaneda</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5256,7 +5224,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785209011</t>
+          <t>1785216972</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5266,7 +5234,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13.814634</t>
+          <t>50.682915</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5283,110 +5251,662 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>0x70f78e17558be5ba081d9ab814282d3372e9da966a3aaa6c4ed300c42444ed89</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.2662</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785216969</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>37.558685</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xaa02396e8bb543b44c5015490aaab7b4d1ea7af3c5dec2d6f7f55b4d52a268fc</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x84f240c88cc0d0fa481bf6894e7a1c197873d29219e094b3b4ccd5e58e0124e1</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785216968</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>16.949153</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x25cf5f7e320c6378a5c8bacd958e6ffaadadf90e7c00f6a15e92c4f9f0b5029b</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785209084</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>10.380488</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xf84a270bf0345ba966197351f609358499391f68d9ec820094d83228f4b6f8a9</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785209068</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>5.42439</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x591377d6be1902f7c3ca69808c2f580f367bef2e314d2686337ca852e8b9150c</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Liga Profesional</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Racing Club de Avellaneda</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0xb3946418880cb00df2cd9c871bccba00e398f3c383d0f89e2699071c1cf7e786</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19493058</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785209011</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785284100</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>13.814634</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>0xffd8b4f29a11a927bd73f04ba1fb11aece522f35d3cd449591ed6067b75fdd94</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>4.81482</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>1.325</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Liga Profesional</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>San Lorenzo de Almagro vs Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>San Lorenzo de Almagro</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Atletico Gimnasia y Esgrima de Mendoza</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>0xfc9c2d415cb9ac9c8405af7288d04b71501bfd44f96ae6045e8ee4b6c621607b</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>L19492342</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>1785186963</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>1785276000</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>14.814831</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
